--- a/Outputs/repeated_holdout_cross_val_50_Breast_Cancer_Winsconsin_recall_minor.xlsx
+++ b/Outputs/repeated_holdout_cross_val_50_Breast_Cancer_Winsconsin_recall_minor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Π.Μ.Σ Στατιστική-Χρηματοοικονομικά και Αναλογιστικά Μαθηματικά\ΜΑΘΗΜΑΤΑ 2ου Εξαμήνου\Εφαρμοσμένη Πολυμεταβλητή Ανάλυση και Big Data\Πτυχιακή\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE46A74D-8D8F-4978-8232-5D0DEBC9CC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB186723-F4C3-4F13-8BE5-D337A9FD37CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shannon" sheetId="1" r:id="rId1"/>
@@ -26,28 +26,27 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Renyi!$B$2:$B$51</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Tsallis!$B$2:$B$51</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">recall_minor!$D$2:$D$51</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">recall_minor!$E$1</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">recall_minor!$E$2:$E$51</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">recall_minor!$F$1</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">recall_minor!$F$2:$F$51</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">recall_minor!$G$1</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">recall_minor!$G$2:$G$51</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Tsallis!$B$2:$B$51</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">recall_minor!$A$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">recall_minor!$A$2:$A$51</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">recall_minor!$B$1</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">recall_minor!$B$2:$B$51</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">recall_minor!$C$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">recall_minor!$C$2:$C$51</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">recall_minor!$D$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">recall_minor!$E$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">recall_minor!$E$2:$E$51</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">recall_minor!$F$1</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">recall_minor!$F$2:$F$51</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">recall_minor!$G$1</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">recall_minor!$G$2:$G$51</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">recall_minor!$A$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">recall_minor!$A$2:$A$51</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">recall_minor!$B$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">recall_minor!$B$2:$B$51</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">recall_minor!$C$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">recall_minor!$C$2:$C$51</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">recall_minor!$D$1</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">recall_minor!$D$2:$D$51</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
   <si>
     <t>accuracy</t>
   </si>
@@ -217,7 +216,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -253,37 +252,37 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.8</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.10</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="4">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.12</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="5">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.14</cx:f>
+        <cx:f>_xlchart.v1.13</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="6">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.16</cx:f>
+        <cx:f>_xlchart.v1.15</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -294,7 +293,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{4ED245C2-B999-4BC1-87FE-F8DA7A815B04}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Shannon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -307,7 +306,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{231B95AB-889C-4B5B-99C7-70BE68CB6C94}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.5</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Renyi</cx:v>
             </cx:txData>
           </cx:tx>
@@ -320,7 +319,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{A34A51F6-B56D-4F2D-902A-EAD22E659172}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.7</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Sharma-Mittal</cx:v>
             </cx:txData>
           </cx:tx>
@@ -333,7 +332,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{29FBAC7C-89F3-4778-9575-9E2B9B45DB82}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.9</cx:f>
+              <cx:f>_xlchart.v1.8</cx:f>
               <cx:v>Tsallis</cx:v>
             </cx:txData>
           </cx:tx>
@@ -346,7 +345,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{2CF782D0-C51D-4A4D-8BB8-6F7DAB3B2EEB}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.11</cx:f>
+              <cx:f>_xlchart.v1.10</cx:f>
               <cx:v>Sharma-Taneja</cx:v>
             </cx:txData>
           </cx:tx>
@@ -359,7 +358,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{77D78166-D72A-4C7C-9A47-C20165717F85}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.13</cx:f>
+              <cx:f>_xlchart.v1.12</cx:f>
               <cx:v>Kapur</cx:v>
             </cx:txData>
           </cx:tx>
@@ -372,7 +371,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{D1EC6F3C-A6F1-429B-8B02-8AAAC50F3DA2}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.15</cx:f>
+              <cx:f>_xlchart.v1.14</cx:f>
               <cx:v>Kaniadakis</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2053,16 +2052,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2098,7 +2097,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5547360" y="262890"/>
+              <a:off x="7330440" y="148590"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2136,16 +2135,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -2181,7 +2180,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5257800" y="240030"/>
+              <a:off x="6918960" y="41910"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2577,10 +2576,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2596,8 +2595,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.93203883495145601</v>
       </c>
@@ -2613,8 +2615,11 @@
       <c r="E2">
         <v>0.90277777777777801</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.95145631067961201</v>
       </c>
@@ -2630,8 +2635,11 @@
       <c r="E3">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.94174757281553401</v>
       </c>
@@ -2647,8 +2655,11 @@
       <c r="E4">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.95145631067961201</v>
       </c>
@@ -2664,8 +2675,11 @@
       <c r="E5">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.970873786407767</v>
       </c>
@@ -2681,8 +2695,11 @@
       <c r="E6">
         <v>0.95890410958904104</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.95631067961165095</v>
       </c>
@@ -2698,8 +2715,11 @@
       <c r="E7">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.95631067961165095</v>
       </c>
@@ -2715,8 +2735,11 @@
       <c r="E8">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.95145631067961201</v>
       </c>
@@ -2732,8 +2755,11 @@
       <c r="E9">
         <v>0.92753623188405798</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.961165048543689</v>
       </c>
@@ -2749,8 +2775,11 @@
       <c r="E10">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.970873786407767</v>
       </c>
@@ -2766,8 +2795,11 @@
       <c r="E11">
         <v>0.95833333333333304</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.94660194174757295</v>
       </c>
@@ -2783,8 +2815,11 @@
       <c r="E12">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.91747572815533995</v>
       </c>
@@ -2800,8 +2835,11 @@
       <c r="E13">
         <v>0.89032258064516101</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.94174757281553401</v>
       </c>
@@ -2817,8 +2855,11 @@
       <c r="E14">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.94660194174757295</v>
       </c>
@@ -2834,8 +2875,11 @@
       <c r="E15">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.961165048543689</v>
       </c>
@@ -2851,8 +2895,11 @@
       <c r="E16">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.95631067961165095</v>
       </c>
@@ -2868,8 +2915,11 @@
       <c r="E17">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.95631067961165095</v>
       </c>
@@ -2885,8 +2935,11 @@
       <c r="E18">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.95631067961165095</v>
       </c>
@@ -2902,8 +2955,11 @@
       <c r="E19">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.961165048543689</v>
       </c>
@@ -2919,8 +2975,11 @@
       <c r="E20">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.94660194174757295</v>
       </c>
@@ -2936,8 +2995,11 @@
       <c r="E21">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.96601941747572795</v>
       </c>
@@ -2953,8 +3015,11 @@
       <c r="E22">
         <v>0.95172413793103405</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.961165048543689</v>
       </c>
@@ -2970,8 +3035,11 @@
       <c r="E23">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.95631067961165095</v>
       </c>
@@ -2987,8 +3055,11 @@
       <c r="E24">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.961165048543689</v>
       </c>
@@ -3004,8 +3075,11 @@
       <c r="E25">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.95631067961165095</v>
       </c>
@@ -3021,8 +3095,11 @@
       <c r="E26">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.96601941747572795</v>
       </c>
@@ -3038,8 +3115,11 @@
       <c r="E27">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.96601941747572795</v>
       </c>
@@ -3055,8 +3135,11 @@
       <c r="E28">
         <v>0.94964028776978404</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.95631067961165095</v>
       </c>
@@ -3072,8 +3155,11 @@
       <c r="E29">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.92718446601941795</v>
       </c>
@@ -3089,8 +3175,11 @@
       <c r="E30">
         <v>0.89361702127659604</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.96601941747572795</v>
       </c>
@@ -3106,8 +3195,11 @@
       <c r="E31">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.94660194174757295</v>
       </c>
@@ -3123,8 +3215,11 @@
       <c r="E32">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.95145631067961201</v>
       </c>
@@ -3140,8 +3235,11 @@
       <c r="E33">
         <v>0.93243243243243201</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95631067961165095</v>
       </c>
@@ -3157,8 +3255,11 @@
       <c r="E34">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.96601941747572795</v>
       </c>
@@ -3174,8 +3275,11 @@
       <c r="E35">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.93689320388349495</v>
       </c>
@@ -3191,8 +3295,11 @@
       <c r="E36">
         <v>0.90780141843971596</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94174757281553401</v>
       </c>
@@ -3208,8 +3315,11 @@
       <c r="E37">
         <v>0.91666666666666696</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.95145631067961201</v>
       </c>
@@ -3225,8 +3335,11 @@
       <c r="E38">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.94660194174757295</v>
       </c>
@@ -3242,8 +3355,11 @@
       <c r="E39">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.95631067961165095</v>
       </c>
@@ -3259,8 +3375,11 @@
       <c r="E40">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.92718446601941795</v>
       </c>
@@ -3276,8 +3395,11 @@
       <c r="E41">
         <v>0.89208633093525203</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.970873786407767</v>
       </c>
@@ -3293,8 +3415,11 @@
       <c r="E42">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.95631067961165095</v>
       </c>
@@ -3310,8 +3435,11 @@
       <c r="E43">
         <v>0.93706293706293697</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.95631067961165095</v>
       </c>
@@ -3327,8 +3455,11 @@
       <c r="E44">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.94660194174757295</v>
       </c>
@@ -3344,8 +3475,11 @@
       <c r="E45">
         <v>0.92517006802721102</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.96601941747572795</v>
       </c>
@@ -3361,8 +3495,11 @@
       <c r="E46">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.93689320388349495</v>
       </c>
@@ -3378,8 +3515,11 @@
       <c r="E47">
         <v>0.90909090909090895</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.94660194174757295</v>
       </c>
@@ -3395,8 +3535,11 @@
       <c r="E48">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94660194174757295</v>
       </c>
@@ -3412,8 +3555,11 @@
       <c r="E49">
         <v>0.92413793103448305</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.93203883495145601</v>
       </c>
@@ -3429,8 +3575,11 @@
       <c r="E50">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.91747572815533995</v>
       </c>
@@ -3445,6 +3594,9 @@
       </c>
       <c r="E51">
         <v>0.87022900763358801</v>
+      </c>
+      <c r="F51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -3455,10 +3607,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3477,8 +3632,11 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.93203883495145601</v>
       </c>
@@ -3497,8 +3655,11 @@
       <c r="F2">
         <v>0.90277777777777801</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.94174757281553401</v>
       </c>
@@ -3517,8 +3678,11 @@
       <c r="F3">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.94174757281553401</v>
       </c>
@@ -3537,8 +3701,11 @@
       <c r="F4">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.93203883495145601</v>
       </c>
@@ -3557,8 +3724,11 @@
       <c r="F5">
         <v>0.90540540540540504</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.94660194174757295</v>
       </c>
@@ -3577,8 +3747,11 @@
       <c r="F6">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.95145631067961201</v>
       </c>
@@ -3597,8 +3770,11 @@
       <c r="F7">
         <v>0.93243243243243201</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.96601941747572795</v>
       </c>
@@ -3617,8 +3793,11 @@
       <c r="F8">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.94660194174757295</v>
       </c>
@@ -3637,8 +3816,11 @@
       <c r="F9">
         <v>0.91851851851851896</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.961165048543689</v>
       </c>
@@ -3657,8 +3839,11 @@
       <c r="F10">
         <v>0.94666666666666699</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.95631067961165095</v>
       </c>
@@ -3677,8 +3862,11 @@
       <c r="F11">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.92718446601941795</v>
       </c>
@@ -3697,8 +3885,11 @@
       <c r="F12">
         <v>0.90066225165562896</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.92233009708737901</v>
       </c>
@@ -3717,8 +3908,11 @@
       <c r="F13">
         <v>0.89743589743589702</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.961165048543689</v>
       </c>
@@ -3737,8 +3931,11 @@
       <c r="F14">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.95631067961165095</v>
       </c>
@@ -3757,8 +3954,11 @@
       <c r="F15">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.92233009708737901</v>
       </c>
@@ -3777,8 +3977,11 @@
       <c r="F16">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.93689320388349495</v>
       </c>
@@ -3797,8 +4000,11 @@
       <c r="F17">
         <v>0.91503267973856195</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.970873786407767</v>
       </c>
@@ -3817,8 +4023,11 @@
       <c r="F18">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.94174757281553401</v>
       </c>
@@ -3837,8 +4046,11 @@
       <c r="F19">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.96601941747572795</v>
       </c>
@@ -3857,8 +4069,11 @@
       <c r="F20">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.95145631067961201</v>
       </c>
@@ -3877,8 +4092,11 @@
       <c r="F21">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.94660194174757295</v>
       </c>
@@ -3897,8 +4115,11 @@
       <c r="F22">
         <v>0.92810457516339895</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.94660194174757295</v>
       </c>
@@ -3917,8 +4138,11 @@
       <c r="F23">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.961165048543689</v>
       </c>
@@ -3937,8 +4161,11 @@
       <c r="F24">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.961165048543689</v>
       </c>
@@ -3957,8 +4184,11 @@
       <c r="F25">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.94174757281553401</v>
       </c>
@@ -3977,8 +4207,11 @@
       <c r="F26">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.93203883495145601</v>
       </c>
@@ -3997,8 +4230,11 @@
       <c r="F27">
         <v>0.90666666666666695</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.961165048543689</v>
       </c>
@@ -4017,8 +4253,11 @@
       <c r="F28">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.94660194174757295</v>
       </c>
@@ -4037,8 +4276,11 @@
       <c r="F29">
         <v>0.927152317880795</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.94174757281553401</v>
       </c>
@@ -4057,8 +4299,11 @@
       <c r="F30">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.970873786407767</v>
       </c>
@@ -4077,8 +4322,11 @@
       <c r="F31">
         <v>0.95890410958904104</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.95145631067961201</v>
       </c>
@@ -4097,8 +4345,11 @@
       <c r="F32">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.95145631067961201</v>
       </c>
@@ -4117,8 +4368,11 @@
       <c r="F33">
         <v>0.93506493506493504</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95145631067961201</v>
       </c>
@@ -4137,8 +4391,11 @@
       <c r="F34">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.97572815533980595</v>
       </c>
@@ -4157,8 +4414,11 @@
       <c r="F35">
         <v>0.96551724137931005</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.93203883495145601</v>
       </c>
@@ -4177,8 +4437,11 @@
       <c r="F36">
         <v>0.90410958904109595</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94174757281553401</v>
       </c>
@@ -4197,8 +4460,11 @@
       <c r="F37">
         <v>0.92105263157894701</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.95145631067961201</v>
       </c>
@@ -4217,8 +4483,11 @@
       <c r="F38">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.91262135922330101</v>
       </c>
@@ -4237,8 +4506,11 @@
       <c r="F39">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.93689320388349495</v>
       </c>
@@ -4257,8 +4529,11 @@
       <c r="F40">
         <v>0.91275167785234901</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.95145631067961201</v>
       </c>
@@ -4277,8 +4552,11 @@
       <c r="F41">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.97572815533980595</v>
       </c>
@@ -4297,8 +4575,11 @@
       <c r="F42">
         <v>0.96644295302013405</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.95145631067961201</v>
       </c>
@@ -4317,8 +4598,11 @@
       <c r="F43">
         <v>0.93243243243243201</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.970873786407767</v>
       </c>
@@ -4337,8 +4621,11 @@
       <c r="F44">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.94174757281553401</v>
       </c>
@@ -4357,8 +4644,11 @@
       <c r="F45">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.94174757281553401</v>
       </c>
@@ -4377,8 +4667,11 @@
       <c r="F46">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.94660194174757295</v>
       </c>
@@ -4397,8 +4690,11 @@
       <c r="F47">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.95145631067961201</v>
       </c>
@@ -4417,8 +4713,11 @@
       <c r="F48">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94174757281553401</v>
       </c>
@@ -4437,8 +4736,11 @@
       <c r="F49">
         <v>0.91304347826086996</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.93203883495145601</v>
       </c>
@@ -4457,8 +4759,11 @@
       <c r="F50">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.94660194174757295</v>
       </c>
@@ -4476,6 +4781,9 @@
       </c>
       <c r="F51">
         <v>0.92413793103448305</v>
+      </c>
+      <c r="G51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -4487,10 +4795,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4512,8 +4820,11 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.93203883495145601</v>
       </c>
@@ -4535,8 +4846,11 @@
       <c r="G2">
         <v>0.90277777777777801</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.94174757281553401</v>
       </c>
@@ -4558,8 +4872,11 @@
       <c r="G3">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.94174757281553401</v>
       </c>
@@ -4581,8 +4898,11 @@
       <c r="G4">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.961165048543689</v>
       </c>
@@ -4604,8 +4924,11 @@
       <c r="G5">
         <v>0.94520547945205502</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.96601941747572795</v>
       </c>
@@ -4627,8 +4950,11 @@
       <c r="G6">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.95145631067961201</v>
       </c>
@@ -4650,8 +4976,11 @@
       <c r="G7">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.95631067961165095</v>
       </c>
@@ -4673,8 +5002,11 @@
       <c r="G8">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.94660194174757295</v>
       </c>
@@ -4696,8 +5028,11 @@
       <c r="G9">
         <v>0.91851851851851896</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.961165048543689</v>
       </c>
@@ -4719,8 +5054,11 @@
       <c r="G10">
         <v>0.94666666666666699</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.95631067961165095</v>
       </c>
@@ -4742,8 +5080,11 @@
       <c r="G11">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.92718446601941795</v>
       </c>
@@ -4765,8 +5106,11 @@
       <c r="G12">
         <v>0.90066225165562896</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.92233009708737901</v>
       </c>
@@ -4788,8 +5132,11 @@
       <c r="G13">
         <v>0.89743589743589702</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.961165048543689</v>
       </c>
@@ -4811,8 +5158,11 @@
       <c r="G14">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.94660194174757295</v>
       </c>
@@ -4834,8 +5184,11 @@
       <c r="G15">
         <v>0.92086330935251803</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.92233009708737901</v>
       </c>
@@ -4857,8 +5210,11 @@
       <c r="G16">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.93689320388349495</v>
       </c>
@@ -4880,8 +5236,11 @@
       <c r="G17">
         <v>0.91503267973856195</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.970873786407767</v>
       </c>
@@ -4903,8 +5262,11 @@
       <c r="G18">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.94174757281553401</v>
       </c>
@@ -4926,8 +5288,11 @@
       <c r="G19">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.96601941747572795</v>
       </c>
@@ -4949,8 +5314,11 @@
       <c r="G20">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.961165048543689</v>
       </c>
@@ -4972,8 +5340,11 @@
       <c r="G21">
         <v>0.94366197183098599</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.94660194174757295</v>
       </c>
@@ -4995,8 +5366,11 @@
       <c r="G22">
         <v>0.92810457516339895</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.94660194174757295</v>
       </c>
@@ -5018,8 +5392,11 @@
       <c r="G23">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.92718446601941795</v>
       </c>
@@ -5041,8 +5418,11 @@
       <c r="G24">
         <v>0.89655172413793105</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.961165048543689</v>
       </c>
@@ -5064,8 +5444,11 @@
       <c r="G25">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.95145631067961201</v>
       </c>
@@ -5087,8 +5470,11 @@
       <c r="G26">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.96601941747572795</v>
       </c>
@@ -5110,8 +5496,11 @@
       <c r="G27">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.961165048543689</v>
       </c>
@@ -5133,8 +5522,11 @@
       <c r="G28">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.94660194174757295</v>
       </c>
@@ -5156,8 +5548,11 @@
       <c r="G29">
         <v>0.927152317880795</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.94174757281553401</v>
       </c>
@@ -5179,8 +5574,11 @@
       <c r="G30">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.95631067961165095</v>
       </c>
@@ -5202,8 +5600,11 @@
       <c r="G31">
         <v>0.93706293706293697</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.961165048543689</v>
       </c>
@@ -5225,8 +5626,11 @@
       <c r="G32">
         <v>0.94666666666666699</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.95631067961165095</v>
       </c>
@@ -5248,8 +5652,11 @@
       <c r="G33">
         <v>0.94117647058823495</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95631067961165095</v>
       </c>
@@ -5271,8 +5678,11 @@
       <c r="G34">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.95631067961165095</v>
       </c>
@@ -5294,8 +5704,11 @@
       <c r="G35">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.94174757281553401</v>
       </c>
@@ -5317,8 +5730,11 @@
       <c r="G36">
         <v>0.91549295774647899</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94174757281553401</v>
       </c>
@@ -5340,8 +5756,11 @@
       <c r="G37">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.95145631067961201</v>
       </c>
@@ -5363,8 +5782,11 @@
       <c r="G38">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.91262135922330101</v>
       </c>
@@ -5386,8 +5808,11 @@
       <c r="G39">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.94660194174757295</v>
       </c>
@@ -5409,8 +5834,11 @@
       <c r="G40">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.94660194174757295</v>
       </c>
@@ -5432,8 +5860,11 @@
       <c r="G41">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.97572815533980595</v>
       </c>
@@ -5455,8 +5886,11 @@
       <c r="G42">
         <v>0.96644295302013405</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.961165048543689</v>
       </c>
@@ -5478,8 +5912,11 @@
       <c r="G43">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.970873786407767</v>
       </c>
@@ -5501,8 +5938,11 @@
       <c r="G44">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.94174757281553401</v>
       </c>
@@ -5524,8 +5964,11 @@
       <c r="G45">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.94174757281553401</v>
       </c>
@@ -5547,8 +5990,11 @@
       <c r="G46">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.94660194174757295</v>
       </c>
@@ -5570,8 +6016,11 @@
       <c r="G47">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.95631067961165095</v>
       </c>
@@ -5593,8 +6042,11 @@
       <c r="G48">
         <v>0.94039735099337796</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94174757281553401</v>
       </c>
@@ -5616,8 +6068,11 @@
       <c r="G49">
         <v>0.91304347826086996</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.92233009708737901</v>
       </c>
@@ -5639,8 +6094,11 @@
       <c r="G50">
         <v>0.89610389610389596</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.94660194174757295</v>
       </c>
@@ -5661,6 +6119,9 @@
       </c>
       <c r="G51">
         <v>0.92413793103448305</v>
+      </c>
+      <c r="H51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -5671,10 +6132,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5693,8 +6154,11 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.94174757281553401</v>
       </c>
@@ -5713,8 +6177,11 @@
       <c r="F2">
         <v>0.91549295774647899</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.95145631067961201</v>
       </c>
@@ -5733,8 +6200,11 @@
       <c r="F3">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.94174757281553401</v>
       </c>
@@ -5753,8 +6223,11 @@
       <c r="F4">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.93689320388349495</v>
       </c>
@@ -5773,8 +6246,11 @@
       <c r="F5">
         <v>0.90510948905109501</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.94660194174757295</v>
       </c>
@@ -5793,8 +6269,11 @@
       <c r="F6">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.95145631067961201</v>
       </c>
@@ -5813,8 +6292,11 @@
       <c r="F7">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.95631067961165095</v>
       </c>
@@ -5833,8 +6315,11 @@
       <c r="F8">
         <v>0.93617021276595702</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.94660194174757295</v>
       </c>
@@ -5853,8 +6338,11 @@
       <c r="F9">
         <v>0.91851851851851896</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.96601941747572795</v>
       </c>
@@ -5873,8 +6361,11 @@
       <c r="F10">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.96601941747572795</v>
       </c>
@@ -5893,8 +6384,11 @@
       <c r="F11">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.94660194174757295</v>
       </c>
@@ -5913,8 +6407,11 @@
       <c r="F12">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.91747572815533995</v>
       </c>
@@ -5933,8 +6430,11 @@
       <c r="F13">
         <v>0.89032258064516101</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.961165048543689</v>
       </c>
@@ -5953,8 +6453,11 @@
       <c r="F14">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.95145631067961201</v>
       </c>
@@ -5973,8 +6476,11 @@
       <c r="F15">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.961165048543689</v>
       </c>
@@ -5993,8 +6499,11 @@
       <c r="F16">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.94174757281553401</v>
       </c>
@@ -6013,8 +6522,11 @@
       <c r="F17">
         <v>0.91549295774647899</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.93203883495145601</v>
       </c>
@@ -6033,8 +6545,11 @@
       <c r="F18">
         <v>0.90277777777777801</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.95631067961165095</v>
       </c>
@@ -6053,8 +6568,11 @@
       <c r="F19">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.961165048543689</v>
       </c>
@@ -6073,8 +6591,11 @@
       <c r="F20">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.94660194174757295</v>
       </c>
@@ -6093,8 +6614,11 @@
       <c r="F21">
         <v>0.92086330935251803</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.96601941747572795</v>
       </c>
@@ -6113,8 +6637,11 @@
       <c r="F22">
         <v>0.95172413793103405</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.95631067961165095</v>
       </c>
@@ -6133,8 +6660,11 @@
       <c r="F23">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.94174757281553401</v>
       </c>
@@ -6153,8 +6683,11 @@
       <c r="F24">
         <v>0.91549295774647899</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.961165048543689</v>
       </c>
@@ -6173,8 +6706,11 @@
       <c r="F25">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.95145631067961201</v>
       </c>
@@ -6193,8 +6729,11 @@
       <c r="F26">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.96601941747572795</v>
       </c>
@@ -6213,8 +6752,11 @@
       <c r="F27">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.980582524271845</v>
       </c>
@@ -6233,8 +6775,11 @@
       <c r="F28">
         <v>0.97222222222222199</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.95631067961165095</v>
       </c>
@@ -6253,8 +6798,11 @@
       <c r="F29">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.94174757281553401</v>
       </c>
@@ -6273,8 +6821,11 @@
       <c r="F30">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.96601941747572795</v>
       </c>
@@ -6293,8 +6844,11 @@
       <c r="F31">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.95145631067961201</v>
       </c>
@@ -6313,8 +6867,11 @@
       <c r="F32">
         <v>0.92957746478873204</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.961165048543689</v>
       </c>
@@ -6333,8 +6890,11 @@
       <c r="F33">
         <v>0.94666666666666699</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95631067961165095</v>
       </c>
@@ -6353,8 +6913,11 @@
       <c r="F34">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.95145631067961201</v>
       </c>
@@ -6373,8 +6936,11 @@
       <c r="F35">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.961165048543689</v>
       </c>
@@ -6393,8 +6959,11 @@
       <c r="F36">
         <v>0.94366197183098599</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94660194174757295</v>
       </c>
@@ -6413,8 +6982,11 @@
       <c r="F37">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.95145631067961201</v>
       </c>
@@ -6433,8 +7005,11 @@
       <c r="F38">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.91747572815533995</v>
       </c>
@@ -6453,8 +7028,11 @@
       <c r="F39">
         <v>0.88111888111888104</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.95631067961165095</v>
       </c>
@@ -6473,8 +7051,11 @@
       <c r="F40">
         <v>0.93617021276595702</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.93689320388349495</v>
       </c>
@@ -6493,8 +7074,11 @@
       <c r="F41">
         <v>0.90780141843971596</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.94174757281553401</v>
       </c>
@@ -6513,8 +7097,11 @@
       <c r="F42">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.961165048543689</v>
       </c>
@@ -6533,8 +7120,11 @@
       <c r="F43">
         <v>0.94366197183098599</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.95631067961165095</v>
       </c>
@@ -6553,8 +7143,11 @@
       <c r="F44">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.92718446601941795</v>
       </c>
@@ -6573,8 +7166,11 @@
       <c r="F45">
         <v>0.89795918367346905</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.96601941747572795</v>
       </c>
@@ -6593,8 +7189,11 @@
       <c r="F46">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.94660194174757295</v>
       </c>
@@ -6613,8 +7212,11 @@
       <c r="F47">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.94660194174757295</v>
       </c>
@@ -6633,8 +7235,11 @@
       <c r="F48">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94174757281553401</v>
       </c>
@@ -6653,8 +7258,11 @@
       <c r="F49">
         <v>0.91304347826086996</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.93203883495145601</v>
       </c>
@@ -6673,8 +7281,11 @@
       <c r="F50">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.92718446601941795</v>
       </c>
@@ -6692,6 +7303,9 @@
       </c>
       <c r="F51">
         <v>0.88888888888888895</v>
+      </c>
+      <c r="G51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -6703,10 +7317,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6728,8 +7342,11 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.93689320388349495</v>
       </c>
@@ -6751,8 +7368,11 @@
       <c r="G2">
         <v>0.90780141843971596</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.95631067961165095</v>
       </c>
@@ -6774,8 +7394,11 @@
       <c r="G3">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.94174757281553401</v>
       </c>
@@ -6797,8 +7420,11 @@
       <c r="G4">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.94174757281553401</v>
       </c>
@@ -6820,8 +7446,11 @@
       <c r="G5">
         <v>0.91304347826086996</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.96601941747572795</v>
       </c>
@@ -6843,8 +7472,11 @@
       <c r="G6">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.95145631067961201</v>
       </c>
@@ -6866,8 +7498,11 @@
       <c r="G7">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.970873786407767</v>
       </c>
@@ -6889,8 +7524,11 @@
       <c r="G8">
         <v>0.95890410958904104</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.94660194174757295</v>
       </c>
@@ -6912,8 +7550,11 @@
       <c r="G9">
         <v>0.91851851851851896</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.96601941747572795</v>
       </c>
@@ -6935,8 +7576,11 @@
       <c r="G10">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.97572815533980595</v>
       </c>
@@ -6958,8 +7602,11 @@
       <c r="G11">
         <v>0.965034965034965</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.95631067961165095</v>
       </c>
@@ -6981,8 +7628,11 @@
       <c r="G12">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.93689320388349495</v>
       </c>
@@ -7004,8 +7654,11 @@
       <c r="G13">
         <v>0.91390728476821204</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.93689320388349495</v>
       </c>
@@ -7027,8 +7680,11 @@
       <c r="G14">
         <v>0.91275167785234901</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.94660194174757295</v>
       </c>
@@ -7050,8 +7706,11 @@
       <c r="G15">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.95145631067961201</v>
       </c>
@@ -7073,8 +7732,11 @@
       <c r="G16">
         <v>0.93506493506493504</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.93689320388349495</v>
       </c>
@@ -7096,8 +7758,11 @@
       <c r="G17">
         <v>0.91390728476821204</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.980582524271845</v>
       </c>
@@ -7119,8 +7784,11 @@
       <c r="G18">
         <v>0.97297297297297303</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.95631067961165095</v>
       </c>
@@ -7142,8 +7810,11 @@
       <c r="G19">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.96601941747572795</v>
       </c>
@@ -7165,8 +7836,11 @@
       <c r="G20">
         <v>0.95172413793103405</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.94660194174757295</v>
       </c>
@@ -7188,8 +7862,11 @@
       <c r="G21">
         <v>0.91970802919707995</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.94660194174757295</v>
       </c>
@@ -7211,8 +7888,11 @@
       <c r="G22">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.95631067961165095</v>
       </c>
@@ -7234,8 +7914,11 @@
       <c r="G23">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.95145631067961201</v>
       </c>
@@ -7257,8 +7940,11 @@
       <c r="G24">
         <v>0.93243243243243201</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.961165048543689</v>
       </c>
@@ -7280,8 +7966,11 @@
       <c r="G25">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.95145631067961201</v>
       </c>
@@ -7303,8 +7992,11 @@
       <c r="G26">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.97572815533980595</v>
       </c>
@@ -7326,8 +8018,11 @@
       <c r="G27">
         <v>0.965034965034965</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.98543689320388395</v>
       </c>
@@ -7349,8 +8044,11 @@
       <c r="G28">
         <v>0.97902097902097895</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.94660194174757295</v>
       </c>
@@ -7372,8 +8070,11 @@
       <c r="G29">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.94174757281553401</v>
       </c>
@@ -7395,8 +8096,11 @@
       <c r="G30">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.96601941747572795</v>
       </c>
@@ -7418,8 +8122,11 @@
       <c r="G31">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.95145631067961201</v>
       </c>
@@ -7441,8 +8148,11 @@
       <c r="G32">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.961165048543689</v>
       </c>
@@ -7464,8 +8174,11 @@
       <c r="G33">
         <v>0.94666666666666699</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95631067961165095</v>
       </c>
@@ -7487,8 +8200,11 @@
       <c r="G34">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.94660194174757295</v>
       </c>
@@ -7510,8 +8226,11 @@
       <c r="G35">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.93203883495145601</v>
       </c>
@@ -7533,8 +8252,11 @@
       <c r="G36">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94174757281553401</v>
       </c>
@@ -7556,8 +8278,11 @@
       <c r="G37">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.95145631067961201</v>
       </c>
@@ -7579,8 +8304,11 @@
       <c r="G38">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.91747572815533995</v>
       </c>
@@ -7602,8 +8330,11 @@
       <c r="G39">
         <v>0.88111888111888104</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.93203883495145601</v>
       </c>
@@ -7625,8 +8356,11 @@
       <c r="G40">
         <v>0.90277777777777801</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.93689320388349495</v>
       </c>
@@ -7648,8 +8382,11 @@
       <c r="G41">
         <v>0.90909090909090895</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.97572815533980595</v>
       </c>
@@ -7671,8 +8408,11 @@
       <c r="G42">
         <v>0.96644295302013405</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.961165048543689</v>
       </c>
@@ -7694,8 +8434,11 @@
       <c r="G43">
         <v>0.94366197183098599</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.95631067961165095</v>
       </c>
@@ -7717,8 +8460,11 @@
       <c r="G44">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.94660194174757295</v>
       </c>
@@ -7740,8 +8486,11 @@
       <c r="G45">
         <v>0.92517006802721102</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.95631067961165095</v>
       </c>
@@ -7763,8 +8512,11 @@
       <c r="G46">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.94660194174757295</v>
       </c>
@@ -7786,8 +8538,11 @@
       <c r="G47">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.95145631067961201</v>
       </c>
@@ -7809,8 +8564,11 @@
       <c r="G48">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94174757281553401</v>
       </c>
@@ -7832,8 +8590,11 @@
       <c r="G49">
         <v>0.91304347826086996</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.93203883495145601</v>
       </c>
@@ -7855,8 +8616,11 @@
       <c r="G50">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.92718446601941795</v>
       </c>
@@ -7877,6 +8641,9 @@
       </c>
       <c r="G51">
         <v>0.88888888888888895</v>
+      </c>
+      <c r="H51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -7887,10 +8654,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7912,8 +8679,11 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.92718446601941795</v>
       </c>
@@ -7935,8 +8705,11 @@
       <c r="G2">
         <v>0.89361702127659604</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.94174757281553401</v>
       </c>
@@ -7958,8 +8731,11 @@
       <c r="G3">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.90291262135922301</v>
       </c>
@@ -7981,8 +8757,11 @@
       <c r="G4">
         <v>0.873417721518987</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.94660194174757295</v>
       </c>
@@ -8004,8 +8783,11 @@
       <c r="G5">
         <v>0.92413793103448305</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.94660194174757295</v>
       </c>
@@ -8027,8 +8809,11 @@
       <c r="G6">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.961165048543689</v>
       </c>
@@ -8050,8 +8835,11 @@
       <c r="G7">
         <v>0.94666666666666699</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.95631067961165095</v>
       </c>
@@ -8073,8 +8861,11 @@
       <c r="G8">
         <v>0.93706293706293697</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.94660194174757295</v>
       </c>
@@ -8096,8 +8887,11 @@
       <c r="G9">
         <v>0.91851851851851896</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.95631067961165095</v>
       </c>
@@ -8119,8 +8913,11 @@
       <c r="G10">
         <v>0.94039735099337796</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.93203883495145601</v>
       </c>
@@ -8142,8 +8939,11 @@
       <c r="G11">
         <v>0.90909090909090895</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.93203883495145601</v>
       </c>
@@ -8165,8 +8965,11 @@
       <c r="G12">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.91747572815533995</v>
       </c>
@@ -8188,8 +8991,11 @@
       <c r="G13">
         <v>0.89032258064516101</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.95631067961165095</v>
       </c>
@@ -8211,8 +9017,11 @@
       <c r="G14">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.95631067961165095</v>
       </c>
@@ -8234,8 +9043,11 @@
       <c r="G15">
         <v>0.93525179856115104</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.94660194174757295</v>
       </c>
@@ -8257,8 +9069,11 @@
       <c r="G16">
         <v>0.92903225806451595</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.93203883495145601</v>
       </c>
@@ -8280,8 +9095,11 @@
       <c r="G17">
         <v>0.91025641025641002</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.96601941747572795</v>
       </c>
@@ -8303,8 +9121,11 @@
       <c r="G18">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.94174757281553401</v>
       </c>
@@ -8326,8 +9147,11 @@
       <c r="G19">
         <v>0.91780821917808197</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.95631067961165095</v>
       </c>
@@ -8349,8 +9173,11 @@
       <c r="G20">
         <v>0.94039735099337796</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.92718446601941795</v>
       </c>
@@ -8372,8 +9199,11 @@
       <c r="G21">
         <v>0.89795918367346905</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.95145631067961201</v>
       </c>
@@ -8395,8 +9225,11 @@
       <c r="G22">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.94660194174757295</v>
       </c>
@@ -8418,8 +9251,11 @@
       <c r="G23">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.93689320388349495</v>
       </c>
@@ -8441,8 +9277,11 @@
       <c r="G24">
         <v>0.90780141843971596</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.94174757281553401</v>
       </c>
@@ -8464,8 +9303,11 @@
       <c r="G25">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.92718446601941795</v>
       </c>
@@ -8487,8 +9329,11 @@
       <c r="G26">
         <v>0.89208633093525203</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.93203883495145601</v>
       </c>
@@ -8510,8 +9355,11 @@
       <c r="G27">
         <v>0.90666666666666695</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.961165048543689</v>
       </c>
@@ -8533,8 +9381,11 @@
       <c r="G28">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.95145631067961201</v>
       </c>
@@ -8556,8 +9407,11 @@
       <c r="G29">
         <v>0.931506849315068</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.94174757281553401</v>
       </c>
@@ -8579,8 +9433,11 @@
       <c r="G30">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.961165048543689</v>
       </c>
@@ -8602,8 +9459,11 @@
       <c r="G31">
         <v>0.94736842105263197</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.94174757281553401</v>
       </c>
@@ -8625,8 +9485,11 @@
       <c r="G32">
         <v>0.92105263157894701</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.95631067961165095</v>
       </c>
@@ -8648,8 +9511,11 @@
       <c r="G33">
         <v>0.94117647058823495</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.961165048543689</v>
       </c>
@@ -8671,8 +9537,11 @@
       <c r="G34">
         <v>0.94520547945205502</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.95631067961165095</v>
       </c>
@@ -8694,8 +9563,11 @@
       <c r="G35">
         <v>0.94039735099337796</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.93203883495145601</v>
       </c>
@@ -8717,8 +9589,11 @@
       <c r="G36">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94174757281553401</v>
       </c>
@@ -8740,8 +9615,11 @@
       <c r="G37">
         <v>0.92105263157894701</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.93689320388349495</v>
       </c>
@@ -8763,8 +9641,11 @@
       <c r="G38">
         <v>0.90780141843971596</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.91747572815533995</v>
       </c>
@@ -8786,8 +9667,11 @@
       <c r="G39">
         <v>0.88111888111888104</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.95631067961165095</v>
       </c>
@@ -8809,8 +9693,11 @@
       <c r="G40">
         <v>0.93706293706293697</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.94174757281553401</v>
       </c>
@@ -8832,8 +9719,11 @@
       <c r="G41">
         <v>0.91666666666666696</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.970873786407767</v>
       </c>
@@ -8855,8 +9745,11 @@
       <c r="G42">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.91747572815533995</v>
       </c>
@@ -8878,8 +9771,11 @@
       <c r="G43">
         <v>0.89171974522292996</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.95631067961165095</v>
       </c>
@@ -8901,8 +9797,11 @@
       <c r="G44">
         <v>0.93959731543624203</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.94660194174757295</v>
       </c>
@@ -8924,8 +9823,11 @@
       <c r="G45">
         <v>0.92517006802721102</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.961165048543689</v>
       </c>
@@ -8947,8 +9849,11 @@
       <c r="G46">
         <v>0.94520547945205502</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.93689320388349495</v>
       </c>
@@ -8970,8 +9875,11 @@
       <c r="G47">
         <v>0.91156462585034004</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.94660194174757295</v>
       </c>
@@ -8993,8 +9901,11 @@
       <c r="G48">
         <v>0.92086330935251803</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94174757281553401</v>
       </c>
@@ -9016,8 +9927,11 @@
       <c r="G49">
         <v>0.91304347826086996</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.93203883495145601</v>
       </c>
@@ -9039,8 +9953,11 @@
       <c r="G50">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.93689320388349495</v>
       </c>
@@ -9061,6 +9978,9 @@
       </c>
       <c r="G51">
         <v>0.90909090909090895</v>
+      </c>
+      <c r="H51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -9071,10 +9991,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9093,8 +10013,11 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0.94660194174757295</v>
       </c>
@@ -9113,8 +10036,11 @@
       <c r="F2">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.95145631067961201</v>
       </c>
@@ -9133,8 +10059,11 @@
       <c r="F3">
         <v>0.93055555555555602</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.94174757281553401</v>
       </c>
@@ -9153,8 +10082,11 @@
       <c r="F4">
         <v>0.91891891891891897</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.95145631067961201</v>
       </c>
@@ -9173,8 +10105,11 @@
       <c r="F5">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.96601941747572795</v>
       </c>
@@ -9193,8 +10128,11 @@
       <c r="F6">
         <v>0.952380952380952</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.95631067961165095</v>
       </c>
@@ -9213,8 +10151,11 @@
       <c r="F7">
         <v>0.93877551020408201</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.95631067961165095</v>
       </c>
@@ -9233,8 +10174,11 @@
       <c r="F8">
         <v>0.93617021276595702</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.95145631067961201</v>
       </c>
@@ -9253,8 +10197,11 @@
       <c r="F9">
         <v>0.92753623188405798</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.970873786407767</v>
       </c>
@@ -9273,8 +10220,11 @@
       <c r="F10">
         <v>0.95890410958904104</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.97572815533980595</v>
       </c>
@@ -9293,8 +10243,11 @@
       <c r="F11">
         <v>0.965034965034965</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.94660194174757295</v>
       </c>
@@ -9313,8 +10266,11 @@
       <c r="F12">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.92233009708737901</v>
       </c>
@@ -9333,8 +10289,11 @@
       <c r="F13">
         <v>0.89610389610389596</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.94174757281553401</v>
       </c>
@@ -9353,8 +10312,11 @@
       <c r="F14">
         <v>0.92105263157894701</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.94660194174757295</v>
       </c>
@@ -9373,8 +10335,11 @@
       <c r="F15">
         <v>0.92307692307692302</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.95145631067961201</v>
       </c>
@@ -9393,8 +10358,11 @@
       <c r="F16">
         <v>0.93421052631578905</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.94660194174757295</v>
       </c>
@@ -9413,8 +10381,11 @@
       <c r="F17">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.95631067961165095</v>
       </c>
@@ -9433,8 +10404,11 @@
       <c r="F18">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.96601941747572795</v>
       </c>
@@ -9453,8 +10427,11 @@
       <c r="F19">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.961165048543689</v>
       </c>
@@ -9473,8 +10450,11 @@
       <c r="F20">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.92233009708737901</v>
       </c>
@@ -9493,8 +10473,11 @@
       <c r="F21">
         <v>0.88571428571428601</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.94174757281553401</v>
       </c>
@@ -9513,8 +10496,11 @@
       <c r="F22">
         <v>0.91549295774647899</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.961165048543689</v>
       </c>
@@ -9533,8 +10519,11 @@
       <c r="F23">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.93689320388349495</v>
       </c>
@@ -9553,8 +10542,11 @@
       <c r="F24">
         <v>0.90780141843971596</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.961165048543689</v>
       </c>
@@ -9573,8 +10565,11 @@
       <c r="F25">
         <v>0.94594594594594605</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.95631067961165095</v>
       </c>
@@ -9593,8 +10588,11 @@
       <c r="F26">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.96601941747572795</v>
       </c>
@@ -9613,8 +10611,11 @@
       <c r="F27">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.970873786407767</v>
       </c>
@@ -9633,8 +10634,11 @@
       <c r="F28">
         <v>0.95774647887323905</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.961165048543689</v>
       </c>
@@ -9653,8 +10657,11 @@
       <c r="F29">
         <v>0.94520547945205502</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.92718446601941795</v>
       </c>
@@ -9673,8 +10680,11 @@
       <c r="F30">
         <v>0.89361702127659604</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.970873786407767</v>
       </c>
@@ -9693,8 +10703,11 @@
       <c r="F31">
         <v>0.95774647887323905</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.95145631067961201</v>
       </c>
@@ -9713,8 +10726,11 @@
       <c r="F32">
         <v>0.92957746478873204</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.96601941747572795</v>
       </c>
@@ -9733,8 +10749,11 @@
       <c r="F33">
         <v>0.95302013422818799</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.95631067961165095</v>
       </c>
@@ -9753,8 +10772,11 @@
       <c r="F34">
         <v>0.93793103448275905</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.97572815533980595</v>
       </c>
@@ -9773,8 +10795,11 @@
       <c r="F35">
         <v>0.965034965034965</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.93689320388349495</v>
       </c>
@@ -9793,8 +10818,11 @@
       <c r="F36">
         <v>0.90647482014388503</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.94660194174757295</v>
       </c>
@@ -9813,8 +10841,11 @@
       <c r="F37">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.961165048543689</v>
       </c>
@@ -9833,8 +10864,11 @@
       <c r="F38">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.94660194174757295</v>
       </c>
@@ -9853,8 +10887,11 @@
       <c r="F39">
         <v>0.92198581560283699</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.93203883495145601</v>
       </c>
@@ -9873,8 +10910,11 @@
       <c r="F40">
         <v>0.90277777777777801</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.961165048543689</v>
       </c>
@@ -9893,8 +10933,11 @@
       <c r="F41">
         <v>0.94444444444444398</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.970873786407767</v>
       </c>
@@ -9913,8 +10956,11 @@
       <c r="F42">
         <v>0.95945945945945998</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.961165048543689</v>
       </c>
@@ -9933,8 +10979,11 @@
       <c r="F43">
         <v>0.94366197183098599</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.95631067961165095</v>
       </c>
@@ -9953,8 +11002,11 @@
       <c r="F44">
         <v>0.93706293706293697</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.93203883495145601</v>
       </c>
@@ -9973,8 +11025,11 @@
       <c r="F45">
         <v>0.90140845070422504</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.96601941747572795</v>
       </c>
@@ -9993,8 +11048,11 @@
       <c r="F46">
         <v>0.95104895104895104</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.94660194174757295</v>
       </c>
@@ -10013,8 +11071,11 @@
       <c r="F47">
         <v>0.92617449664429496</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.95145631067961201</v>
       </c>
@@ -10033,8 +11094,11 @@
       <c r="F48">
         <v>0.92857142857142905</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.94660194174757295</v>
       </c>
@@ -10053,8 +11117,11 @@
       <c r="F49">
         <v>0.92413793103448305</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.93203883495145601</v>
       </c>
@@ -10073,8 +11140,11 @@
       <c r="F50">
         <v>0.90789473684210498</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.92718446601941795</v>
       </c>
@@ -10092,6 +11162,9 @@
       </c>
       <c r="F51">
         <v>0.88888888888888895</v>
+      </c>
+      <c r="G51">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
